--- a/data/trans_camb/P19C08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C08-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,86</t>
+          <t>-0,58; 3,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,33</t>
+          <t>-1,42; 0,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,66</t>
+          <t>-1,31; 0,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,93</t>
+          <t>-1,49; 0,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,0</t>
+          <t>-1,91; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,72</t>
+          <t>-1,36; 0,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,58</t>
+          <t>-0,48; 1,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,15</t>
+          <t>-1,05; 0,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,54</t>
+          <t>-0,87; 0,5</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-80,42; 841,22</t>
+          <t>-68,73; 912,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-81,01; 344,59</t>
+          <t>-82,36; 359,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,94</t>
+          <t>-1,53; 0,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 0,0</t>
+          <t>-1,84; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,47</t>
+          <t>-1,51; 0,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,62</t>
+          <t>-2,55; 0,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,13</t>
+          <t>-2,75; 0,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 0,19</t>
+          <t>-2,7; 0,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,51</t>
+          <t>-1,47; 0,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; -0,24</t>
+          <t>-1,75; -0,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,13</t>
+          <t>-1,7; 0,02</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 218,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-96,54; 229,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,5; 152,56</t>
+          <t>-87,33; 112,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 140,83</t>
+          <t>-100,0; 75,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-91,43; 63,71</t>
+          <t>-91,52; 42,96</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,59</t>
+          <t>0,11; 1,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,79</t>
+          <t>0,0; 5,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,34</t>
+          <t>0,09; 1,26</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1325,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,46</t>
+          <t>-0,64; 0,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,22</t>
+          <t>-0,76; 0,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,09</t>
+          <t>-0,78; 0,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,19</t>
+          <t>-0,35; 1,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1350,22 +1350,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,82</t>
+          <t>-0,55; 0,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,55</t>
+          <t>-0,29; 0,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,09</t>
+          <t>-0,59; 0,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,33</t>
+          <t>-0,45; 0,33</t>
         </is>
       </c>
     </row>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,67; 351,5</t>
+          <t>-58,78; 596,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 193,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-80,27; 258,26</t>
+          <t>-79,41; 279,84</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,61</t>
+          <t>0,47; 2,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1551,37 +1551,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>0,0; 4,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,8</t>
+          <t>-1,46; 0,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,46</t>
+          <t>-1,82; 0,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; -0,1</t>
+          <t>-2,38; -0,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,1</t>
+          <t>-0,65; 1,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,31</t>
+          <t>-1,08; 0,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,77</t>
+          <t>-0,95; 0,73</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 666,28</t>
+          <t>-73,7; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,86</t>
+          <t>-1,41; 0,85</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,0</t>
+          <t>-2,5; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,0</t>
+          <t>-2,26; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,03</t>
+          <t>-0,24; 1,12</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,88; -0,1</t>
+          <t>-0,94; -0,1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,7</t>
+          <t>-0,41; 0,76</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,86</t>
+          <t>-0,32; 0,89</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,03; -0,1</t>
+          <t>-0,91; -0,08</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,47</t>
+          <t>-0,58; 0,39</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-69,06; —</t>
+          <t>-64,92; 1130,22</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-83,4; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 696,27</t>
+          <t>-63,66; 707,84</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-84,43; 465,68</t>
+          <t>-86,3; 390,29</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,69</t>
+          <t>-0,08; 0,71</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,08</t>
+          <t>-0,49; 0,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 0,47</t>
+          <t>-0,26; 0,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,46</t>
+          <t>-0,35; 0,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,7; -0,03</t>
+          <t>-0,66; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,16</t>
+          <t>-0,54; 0,16</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,49</t>
+          <t>-0,12; 0,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,48; -0,05</t>
+          <t>-0,5; -0,06</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,2</t>
+          <t>-0,36; 0,19</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 369,95</t>
+          <t>-26,46; 347,99</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-89,73; 62,62</t>
+          <t>-89,98; 75,58</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-57,09; 243,01</t>
+          <t>-56,36; 244,36</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-45,66; 132,09</t>
+          <t>-47,83; 127,88</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-90,82; 12,5</t>
+          <t>-87,57; 13,39</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-66,54; 54,36</t>
+          <t>-64,16; 57,17</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 173,36</t>
+          <t>-20,8; 136,97</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-83,68; -9,52</t>
+          <t>-82,81; -9,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 59,08</t>
+          <t>-55,63; 63,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C08-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>-0,04</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,18</t>
+          <t>-0,58; 2,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,54</t>
+          <t>-1,44; 0,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,66</t>
+          <t>-1,41; 0,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,67</t>
+          <t>-1,42; 0,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,0</t>
+          <t>-1,9; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,68</t>
+          <t>-1,11; 0,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,59</t>
+          <t>-0,56; 1,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,15</t>
+          <t>-1,12; 0,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,5</t>
+          <t>-0,81; 0,54</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-30,19%</t>
+          <t>-27,84%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-17,02%</t>
+          <t>-7,68%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,21; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-68,73; 912,46</t>
+          <t>-76,2; 776,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-82,36; 359,31</t>
+          <t>-81,02; 337,24</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,65</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,88</t>
+          <t>-1,26; 0,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,0</t>
+          <t>-1,99; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,46</t>
+          <t>-1,44; 0,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,45</t>
+          <t>-2,5; 0,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,03</t>
+          <t>-2,91; 0,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 0,35</t>
+          <t>-2,77; 0,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,31</t>
+          <t>-1,53; 0,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; -0,13</t>
+          <t>-1,77; -0,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,02</t>
+          <t>-1,75; 0,05</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-47,13%</t>
+          <t>-45,71%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-64,54%</t>
+          <t>-66,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-61,02%</t>
+          <t>-61,98%</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 218,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-96,54; 229,1</t>
+          <t>-100,0; 115,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-87,33; 112,46</t>
+          <t>-89,4; 160,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,65</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-91,52; 42,96</t>
+          <t>-91,26; 44,08</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,66</t>
+          <t>0,35; 2,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,03</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,17</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,18</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,11</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,26</t>
+          <t>0,3; 1,67</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,42</t>
+          <t>-0,57; 0,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,14</t>
+          <t>-0,75; 0,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,09</t>
+          <t>-0,51; 0,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,1</t>
+          <t>-0,41; 1,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,34</t>
+          <t>-0,85; 0,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,85</t>
+          <t>-0,48; 0,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,55</t>
+          <t>-0,31; 0,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,15</t>
+          <t>-0,6; 0,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,33</t>
+          <t>-0,31; 0,57</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-68,44%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-12,15%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-92,91; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-58,78; 596,03</t>
+          <t>-63,53; 512,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-79,41; 279,84</t>
+          <t>-67,95; 466,43</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,64</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,09</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,63</t>
+          <t>0,47; 2,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,79</t>
+          <t>-1,64; 0,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,39</t>
+          <t>-1,81; 0,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,03</t>
+          <t>-2,27; 0,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,12</t>
+          <t>-0,64; 1,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,35</t>
+          <t>-1,15; 0,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,73</t>
+          <t>-0,97; 0,76</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-87,59%</t>
+          <t>-78,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-16,06%</t>
+          <t>-16,48%</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-73,7; —</t>
+          <t>-70,24; 658,67</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -1757,22 +1757,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,85</t>
+          <t>-1,42; 0,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,0</t>
+          <t>-2,32; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,0</t>
+          <t>-2,04; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,12</t>
+          <t>-0,27; 1,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,76</t>
+          <t>-0,44; 0,84</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,89</t>
+          <t>-0,33; 0,86</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,91; -0,08</t>
+          <t>-0,92; -0,1</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,39</t>
+          <t>-0,48; 0,62</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-2,0%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-64,92; 1130,22</t>
+          <t>-73,39; 1056,29</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,51; 1022,13</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-63,66; 707,84</t>
+          <t>-60,24; 572,58</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-86,3; 390,29</t>
+          <t>-80,44; 519,75</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -1973,37 +1973,37 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,71</t>
+          <t>-0,07; 0,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,07</t>
+          <t>-0,49; 0,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,46</t>
+          <t>-0,17; 0,6</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,44</t>
+          <t>-0,34; 0,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,0</t>
+          <t>-0,67; 0,01</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,16</t>
+          <t>-0,46; 0,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 0,46</t>
+          <t>-0,14; 0,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,19</t>
+          <t>-0,21; 0,29</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-28,49%</t>
+          <t>-15,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-10,23%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 347,99</t>
+          <t>-21,34; 340,93</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-89,98; 75,58</t>
+          <t>-90,92; 63,35</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-56,36; 244,36</t>
+          <t>-41,67; 297,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-47,83; 127,88</t>
+          <t>-46,25; 133,31</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-87,57; 13,39</t>
+          <t>-89,32; 18,65</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-64,16; 57,17</t>
+          <t>-59,16; 68,5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 136,97</t>
+          <t>-22,37; 141,23</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-82,81; -9,96</t>
+          <t>-82,54; -11,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-55,63; 63,77</t>
+          <t>-37,78; 97,6</t>
         </is>
       </c>
     </row>
